--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3004-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3004-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{402AF7A1-54FF-4349-B234-8BC24BA83912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA9D480C-4CB8-4C69-BC66-4E2BC7EFCB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{657362E4-B720-491B-BD07-105373ABBB19}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{345AEFF1-F044-4DE3-A86C-2A3CA9E4D542}"/>
   </bookViews>
   <sheets>
     <sheet name="3004-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1448,29 +1448,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AA4F818-2A91-4D93-9C3D-FB22AA9F8165}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B7AF711-CCDD-4C9C-9597-E0A25E0A4E50}">
   <dimension ref="A1:X31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1504,7 +1503,7 @@
       <c r="W1" s="26"/>
       <c r="X1" s="18"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1540,7 +1539,7 @@
       <c r="W2" s="28"/>
       <c r="X2" s="29"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1592,7 +1591,7 @@
       </c>
       <c r="X3" s="32"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1660,7 +1659,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>2024</v>
       </c>
@@ -1732,7 +1731,7 @@
         <v>4.09</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>2023</v>
       </c>
@@ -1804,7 +1803,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>2022</v>
       </c>
@@ -1876,7 +1875,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>2021</v>
       </c>
@@ -1948,7 +1947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>2020</v>
       </c>
@@ -2020,7 +2019,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2019</v>
       </c>
@@ -2092,7 +2091,7 @@
         <v>6.44</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
         <v>2018</v>
       </c>
@@ -2164,7 +2163,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2017</v>
       </c>
@@ -2236,7 +2235,7 @@
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>2016</v>
       </c>
@@ -2308,7 +2307,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2015</v>
       </c>
@@ -2380,7 +2379,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="33">
         <v>2014</v>
       </c>
@@ -2452,7 +2451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2013</v>
       </c>
@@ -2524,7 +2523,7 @@
         <v>2.88</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
         <v>2012</v>
       </c>
@@ -2596,7 +2595,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2011</v>
       </c>
@@ -2668,7 +2667,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="33">
         <v>2010</v>
       </c>
@@ -2740,7 +2739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2009</v>
       </c>
@@ -2812,7 +2811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="33">
         <v>2008</v>
       </c>
@@ -2884,7 +2883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2007</v>
       </c>
@@ -2956,7 +2955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="33">
         <v>2006</v>
       </c>
@@ -3028,7 +3027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2005</v>
       </c>
@@ -3100,7 +3099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="33">
         <v>2004</v>
       </c>
@@ -3172,7 +3171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2003</v>
       </c>
@@ -3244,7 +3243,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
         <v>2002</v>
       </c>
@@ -3316,7 +3315,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2001</v>
       </c>
@@ -3388,7 +3387,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
         <v>2000</v>
       </c>
@@ -3460,7 +3459,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>1999</v>
       </c>
@@ -3532,7 +3531,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="33" t="s">
         <v>42</v>
       </c>
